--- a/data/MAPS.MI.xlsx
+++ b/data/MAPS.MI.xlsx
@@ -44279,6 +44279,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1910">
+      <c r="A1910" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1910" t="n">
+        <v>8806</v>
+      </c>
+      <c r="C1910" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="D1910" t="n">
+        <v>2.58999991416931</v>
+      </c>
+      <c r="E1910" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="F1910" t="n">
+        <v>2.58999991416931</v>
+      </c>
+      <c r="G1910" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MAPS.MI.xlsx
+++ b/data/MAPS.MI.xlsx
@@ -44302,6 +44302,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1911">
+      <c r="A1911" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1911" t="n">
+        <v>154500</v>
+      </c>
+      <c r="C1911" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="D1911" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="E1911" t="n">
+        <v>2.58999991416931</v>
+      </c>
+      <c r="F1911" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="G1911" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MAPS.MI.xlsx
+++ b/data/MAPS.MI.xlsx
@@ -44325,6 +44325,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1912">
+      <c r="A1912" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1912" t="n">
+        <v>12240</v>
+      </c>
+      <c r="C1912" t="n">
+        <v>2.58999991416931</v>
+      </c>
+      <c r="D1912" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="E1912" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="F1912" t="n">
+        <v>2.58999991416931</v>
+      </c>
+      <c r="G1912" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MAPS.MI.xlsx
+++ b/data/MAPS.MI.xlsx
@@ -44348,6 +44348,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1913">
+      <c r="A1913" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1913" t="n">
+        <v>11766</v>
+      </c>
+      <c r="C1913" t="n">
+        <v>2.58999991416931</v>
+      </c>
+      <c r="D1913" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E1913" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="F1913" t="n">
+        <v>2.5699999332428</v>
+      </c>
+      <c r="G1913" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MAPS.MI.xlsx
+++ b/data/MAPS.MI.xlsx
@@ -44189,22 +44189,22 @@
     </row>
     <row r="1906">
       <c r="A1906" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1906" t="n">
-        <v>24740</v>
+        <v>7620</v>
       </c>
       <c r="C1906" t="n">
-        <v>2.64000010490417</v>
+        <v>2.58999991416931</v>
       </c>
       <c r="D1906" t="n">
-        <v>2.5699999332428</v>
+        <v>2.53999996185303</v>
       </c>
       <c r="E1906" t="n">
-        <v>2.5699999332428</v>
+        <v>2.53999996185303</v>
       </c>
       <c r="F1906" t="n">
-        <v>2.59999990463257</v>
+        <v>2.58999991416931</v>
       </c>
       <c r="G1906" t="s">
         <v>7</v>
@@ -44212,22 +44212,22 @@
     </row>
     <row r="1907">
       <c r="A1907" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1907" t="n">
-        <v>2100</v>
+        <v>24740</v>
       </c>
       <c r="C1907" t="n">
-        <v>2.63000011444092</v>
+        <v>2.64000010490417</v>
       </c>
       <c r="D1907" t="n">
-        <v>2.58999991416931</v>
+        <v>2.5699999332428</v>
       </c>
       <c r="E1907" t="n">
-        <v>2.58999991416931</v>
+        <v>2.5699999332428</v>
       </c>
       <c r="F1907" t="n">
-        <v>2.63000011444092</v>
+        <v>2.59999990463257</v>
       </c>
       <c r="G1907" t="s">
         <v>7</v>
@@ -44235,19 +44235,19 @@
     </row>
     <row r="1908">
       <c r="A1908" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1908" t="n">
-        <v>2</v>
+        <v>2100</v>
       </c>
       <c r="C1908" t="n">
         <v>2.63000011444092</v>
       </c>
       <c r="D1908" t="n">
-        <v>2.63000011444092</v>
+        <v>2.58999991416931</v>
       </c>
       <c r="E1908" t="n">
-        <v>2.63000011444092</v>
+        <v>2.58999991416931</v>
       </c>
       <c r="F1908" t="n">
         <v>2.63000011444092</v>
@@ -44258,19 +44258,19 @@
     </row>
     <row r="1909">
       <c r="A1909" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1909" t="n">
-        <v>520</v>
+        <v>2</v>
       </c>
       <c r="C1909" t="n">
         <v>2.63000011444092</v>
       </c>
       <c r="D1909" t="n">
-        <v>2.55999994277954</v>
+        <v>2.63000011444092</v>
       </c>
       <c r="E1909" t="n">
-        <v>2.59999990463257</v>
+        <v>2.63000011444092</v>
       </c>
       <c r="F1909" t="n">
         <v>2.63000011444092</v>
@@ -44281,22 +44281,22 @@
     </row>
     <row r="1910">
       <c r="A1910" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1910" t="n">
-        <v>8806</v>
+        <v>520</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.59999990463257</v>
+        <v>2.63000011444092</v>
       </c>
       <c r="D1910" t="n">
-        <v>2.58999991416931</v>
+        <v>2.55999994277954</v>
       </c>
       <c r="E1910" t="n">
         <v>2.59999990463257</v>
       </c>
       <c r="F1910" t="n">
-        <v>2.58999991416931</v>
+        <v>2.63000011444092</v>
       </c>
       <c r="G1910" t="s">
         <v>7</v>
@@ -44304,22 +44304,22 @@
     </row>
     <row r="1911">
       <c r="A1911" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1911" t="n">
-        <v>154500</v>
+        <v>8806</v>
       </c>
       <c r="C1911" t="n">
         <v>2.59999990463257</v>
       </c>
       <c r="D1911" t="n">
-        <v>2.54999995231628</v>
+        <v>2.58999991416931</v>
       </c>
       <c r="E1911" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="F1911" t="n">
         <v>2.58999991416931</v>
-      </c>
-      <c r="F1911" t="n">
-        <v>2.59999990463257</v>
       </c>
       <c r="G1911" t="s">
         <v>7</v>
@@ -44327,22 +44327,22 @@
     </row>
     <row r="1912">
       <c r="A1912" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1912" t="n">
-        <v>12240</v>
+        <v>154500</v>
       </c>
       <c r="C1912" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="D1912" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="E1912" t="n">
         <v>2.58999991416931</v>
       </c>
-      <c r="D1912" t="n">
-        <v>2.51999998092651</v>
-      </c>
-      <c r="E1912" t="n">
-        <v>2.54999995231628</v>
-      </c>
       <c r="F1912" t="n">
-        <v>2.58999991416931</v>
+        <v>2.59999990463257</v>
       </c>
       <c r="G1912" t="s">
         <v>7</v>
@@ -44350,24 +44350,47 @@
     </row>
     <row r="1913">
       <c r="A1913" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1913" t="n">
-        <v>11766</v>
+        <v>12240</v>
       </c>
       <c r="C1913" t="n">
         <v>2.58999991416931</v>
       </c>
       <c r="D1913" t="n">
-        <v>2.5</v>
+        <v>2.51999998092651</v>
       </c>
       <c r="E1913" t="n">
-        <v>2.57999992370605</v>
+        <v>2.54999995231628</v>
       </c>
       <c r="F1913" t="n">
-        <v>2.5699999332428</v>
+        <v>2.58999991416931</v>
       </c>
       <c r="G1913" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1914" t="n">
+        <v>11581</v>
+      </c>
+      <c r="C1914" t="n">
+        <v>2.52999997138977</v>
+      </c>
+      <c r="D1914" t="n">
+        <v>2.49000000953674</v>
+      </c>
+      <c r="E1914" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="F1914" t="n">
+        <v>2.52999997138977</v>
+      </c>
+      <c r="G1914" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MAPS.MI.xlsx
+++ b/data/MAPS.MI.xlsx
@@ -50191,6 +50191,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1917">
+      <c r="A1917" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1917" t="n">
+        <v>1020</v>
+      </c>
+      <c r="C1917" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="D1917" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="E1917" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="F1917" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="G1917" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="H1917" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MAPS.MI.xlsx
+++ b/data/MAPS.MI.xlsx
@@ -50217,6 +50217,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1918">
+      <c r="A1918" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1918" t="n">
+        <v>43640</v>
+      </c>
+      <c r="C1918" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D1918" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="E1918" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F1918" t="n">
+        <v>2.45000004768372</v>
+      </c>
+      <c r="G1918" t="n">
+        <v>2.45000004768372</v>
+      </c>
+      <c r="H1918" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MAPS.MI.xlsx
+++ b/data/MAPS.MI.xlsx
@@ -50243,6 +50243,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1919">
+      <c r="A1919" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1919" t="n">
+        <v>27923</v>
+      </c>
+      <c r="C1919" t="n">
+        <v>2.42000007629395</v>
+      </c>
+      <c r="D1919" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="E1919" t="n">
+        <v>2.42000007629395</v>
+      </c>
+      <c r="F1919" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="G1919" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="H1919" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MAPS.MI.xlsx
+++ b/data/MAPS.MI.xlsx
@@ -50269,6 +50269,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1920">
+      <c r="A1920" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1920" t="n">
+        <v>4347</v>
+      </c>
+      <c r="C1920" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="D1920" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="E1920" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="F1920" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="G1920" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="H1920" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MAPS.MI.xlsx
+++ b/data/MAPS.MI.xlsx
@@ -50347,6 +50347,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1923">
+      <c r="A1923" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1923" t="n">
+        <v>2301</v>
+      </c>
+      <c r="C1923" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="D1923" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="E1923" t="n">
+        <v>2.33999991416931</v>
+      </c>
+      <c r="F1923" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="G1923" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="H1923" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MAPS.MI.xlsx
+++ b/data/MAPS.MI.xlsx
@@ -44663,8 +44663,31 @@
       <c r="E1926" t="n">
         <v>2.36999988555908</v>
       </c>
-      <c r="F1926"/>
+      <c r="F1926" t="n">
+        <v>2.33999991416931</v>
+      </c>
       <c r="G1926" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1927" t="n">
+        <v>7263</v>
+      </c>
+      <c r="C1927" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="D1927" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="E1927" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="F1927"/>
+      <c r="G1927" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MAPS.MI.xlsx
+++ b/data/MAPS.MI.xlsx
@@ -44686,8 +44686,31 @@
       <c r="E1927" t="n">
         <v>2.34999990463257</v>
       </c>
-      <c r="F1927"/>
+      <c r="F1927" t="n">
+        <v>2.34999990463257</v>
+      </c>
       <c r="G1927" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1928" t="n">
+        <v>623</v>
+      </c>
+      <c r="C1928" t="n">
+        <v>2.36999988555908</v>
+      </c>
+      <c r="D1928" t="n">
+        <v>2.32999992370605</v>
+      </c>
+      <c r="E1928" t="n">
+        <v>2.36999988555908</v>
+      </c>
+      <c r="F1928"/>
+      <c r="G1928" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MAPS.MI.xlsx
+++ b/data/MAPS.MI.xlsx
@@ -44709,7 +44709,9 @@
       <c r="E1928" t="n">
         <v>2.36999988555908</v>
       </c>
-      <c r="F1928"/>
+      <c r="F1928" t="n">
+        <v>2.36999988555908</v>
+      </c>
       <c r="G1928" t="s">
         <v>7</v>
       </c>

--- a/data/MAPS.MI.xlsx
+++ b/data/MAPS.MI.xlsx
@@ -44716,6 +44716,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1929">
+      <c r="A1929" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1929" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1929" t="n">
+        <v>2.36999988555908</v>
+      </c>
+      <c r="D1929" t="n">
+        <v>2.36999988555908</v>
+      </c>
+      <c r="E1929" t="n">
+        <v>2.36999988555908</v>
+      </c>
+      <c r="F1929" t="n">
+        <v>2.36999988555908</v>
+      </c>
+      <c r="G1929" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1930" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C1930" t="n">
+        <v>2.36999988555908</v>
+      </c>
+      <c r="D1930" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="E1930" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="F1930"/>
+      <c r="G1930" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MAPS.MI.xlsx
+++ b/data/MAPS.MI.xlsx
@@ -44762,6 +44762,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1931">
+      <c r="A1931" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1931" t="n">
+        <v>112</v>
+      </c>
+      <c r="C1931" t="n">
+        <v>2.36999988555908</v>
+      </c>
+      <c r="D1931" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="E1931" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="F1931" t="n">
+        <v>2.36999988555908</v>
+      </c>
+      <c r="G1931" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MAPS.MI.xlsx
+++ b/data/MAPS.MI.xlsx
@@ -50633,6 +50633,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1934">
+      <c r="A1934" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1934" t="n">
+        <v>12897</v>
+      </c>
+      <c r="C1934" t="n">
+        <v>2.28999996185303</v>
+      </c>
+      <c r="D1934" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="E1934" t="n">
+        <v>2.28999996185303</v>
+      </c>
+      <c r="F1934" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G1934" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H1934" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MAPS.MI.xlsx
+++ b/data/MAPS.MI.xlsx
@@ -50659,6 +50659,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1935">
+      <c r="A1935" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1935" t="n">
+        <v>23751</v>
+      </c>
+      <c r="C1935" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="D1935" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E1935" t="n">
+        <v>2.28999996185303</v>
+      </c>
+      <c r="F1935" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="G1935" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="H1935" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MAPS.MI.xlsx
+++ b/data/MAPS.MI.xlsx
@@ -56493,6 +56493,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1936">
+      <c r="A1936" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1936" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1936" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="D1936" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="E1936" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="F1936" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="G1936" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="H1936" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1936" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1937" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1937" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D1937" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="E1937" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F1937" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="G1937" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="H1937" t="n">
+        <v>3126</v>
+      </c>
+      <c r="I1937" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MAPS.MI.xlsx
+++ b/data/MAPS.MI.xlsx
@@ -56551,6 +56551,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1938">
+      <c r="A1938" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1938" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1938" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="D1938" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="E1938" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="F1938" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="G1938" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="H1938" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1938" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MAPS.MI.xlsx
+++ b/data/MAPS.MI.xlsx
@@ -56580,6 +56580,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1939">
+      <c r="A1939" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1939" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1939" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="D1939" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="E1939" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="F1939" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="G1939" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="H1939" t="n">
+        <v>100</v>
+      </c>
+      <c r="I1939" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MAPS.MI.xlsx
+++ b/data/MAPS.MI.xlsx
@@ -56609,6 +56609,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1940">
+      <c r="A1940" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1940" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1940" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="D1940" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="E1940" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="F1940" t="n">
+        <v>2.30999994277954</v>
+      </c>
+      <c r="G1940" t="n">
+        <v>2.30999994277954</v>
+      </c>
+      <c r="H1940" t="n">
+        <v>20</v>
+      </c>
+      <c r="I1940" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MAPS.MI.xlsx
+++ b/data/MAPS.MI.xlsx
@@ -56617,13 +56617,13 @@
         <v>46318.2916666667</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.29999995231628</v>
+        <v>2.30999994277954</v>
       </c>
       <c r="D1940" t="n">
-        <v>2.29999995231628</v>
+        <v>2.30999994277954</v>
       </c>
       <c r="E1940" t="n">
-        <v>2.29999995231628</v>
+        <v>2.30999994277954</v>
       </c>
       <c r="F1940" t="n">
         <v>2.30999994277954</v>
@@ -56635,6 +56635,35 @@
         <v>20</v>
       </c>
       <c r="I1940" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1941" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1941" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="D1941" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="E1941" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="F1941" t="n">
+        <v>2.30999994277954</v>
+      </c>
+      <c r="G1941" t="n">
+        <v>2.30999994277954</v>
+      </c>
+      <c r="H1941" t="n">
+        <v>24</v>
+      </c>
+      <c r="I1941" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MAPS.MI.xlsx
+++ b/data/MAPS.MI.xlsx
@@ -56649,7 +56649,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="D1941" t="n">
-        <v>2.29999995231628</v>
+        <v>2.30999994277954</v>
       </c>
       <c r="E1941" t="n">
         <v>2.29999995231628</v>
@@ -56664,6 +56664,35 @@
         <v>24</v>
       </c>
       <c r="I1941" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1942" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1942" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D1942" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="E1942" t="n">
+        <v>2.24000000953674</v>
+      </c>
+      <c r="F1942" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="G1942" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="H1942" t="n">
+        <v>5502</v>
+      </c>
+      <c r="I1942" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MAPS.MI.xlsx
+++ b/data/MAPS.MI.xlsx
@@ -56696,6 +56696,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1943">
+      <c r="A1943" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1943" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1943" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="D1943" t="n">
+        <v>2.29999995231628</v>
+      </c>
+      <c r="E1943" t="n">
+        <v>2.23000001907349</v>
+      </c>
+      <c r="F1943" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="G1943" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="H1943" t="n">
+        <v>3021</v>
+      </c>
+      <c r="I1943" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MAPS.MI.xlsx
+++ b/data/MAPS.MI.xlsx
@@ -56725,6 +56725,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1944">
+      <c r="A1944" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1944" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1944" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="D1944" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="E1944" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="F1944" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="G1944" t="n">
+        <v>2.27999997138977</v>
+      </c>
+      <c r="H1944" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1944" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1945" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1945" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="D1945" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="E1945" t="n">
+        <v>2.23000001907349</v>
+      </c>
+      <c r="F1945" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="G1945" t="n">
+        <v>2.25999999046326</v>
+      </c>
+      <c r="H1945" t="n">
+        <v>1827</v>
+      </c>
+      <c r="I1945" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
